--- a/Test Data.xlsx
+++ b/Test Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://engie-my.sharepoint.com/personal/jn6484_engie_com/Documents/Documents/TestComplete 15 Projects/MyEngie/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\MyEngie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{7FAF35D1-F7CD-440A-90A3-799737A06A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B71354C-4842-452A-BD4B-6454C26E34C1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2505848-6198-4699-846A-F17BC4BCD8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="100" windowWidth="19190" windowHeight="10070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Browser" sheetId="9" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="191">
   <si>
     <t>Sl.No</t>
   </si>
@@ -585,9 +585,6 @@
     <t>Add_Fuel_WA_Customer</t>
   </si>
   <si>
-    <t>sravani@noesyssoftware.com</t>
-  </si>
-  <si>
     <t>02-02-1992</t>
   </si>
   <si>
@@ -606,7 +603,16 @@
     <t>testing234@gmail.com</t>
   </si>
   <si>
-    <t>testing678@gmail.com</t>
+    <t>ramya@noesyssoftware.com</t>
+  </si>
+  <si>
+    <t>muttu@gmail.com</t>
+  </si>
+  <si>
+    <t>muttu1@gmail.com</t>
+  </si>
+  <si>
+    <t>muttu2@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1457,7 +1463,7 @@
         <v>70</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F8" s="14">
         <v>40426020</v>
@@ -1466,7 +1472,7 @@
         <v>2010</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1481,7 +1487,7 @@
         <v>70</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F9" s="14">
         <v>30061825</v>
@@ -1708,7 +1714,7 @@
         <v>5162</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
@@ -1756,7 +1762,7 @@
         <v>3021</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -2057,7 +2063,7 @@
         <v>70</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F33" s="14">
         <v>27608078</v>
@@ -2277,7 +2283,7 @@
         <v>70</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F42" s="14">
         <v>21696233</v>
@@ -2297,7 +2303,7 @@
         <v>70</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
@@ -2315,7 +2321,7 @@
         <v>70</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F44" s="14">
         <v>21731062</v>
@@ -2335,7 +2341,7 @@
         <v>70</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F45" s="14"/>
       <c r="G45" s="14"/>
@@ -2355,7 +2361,7 @@
         <v>70</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F46" s="14">
         <v>30460919</v>
@@ -2375,7 +2381,7 @@
         <v>70</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F47" s="14"/>
       <c r="G47" s="14"/>
@@ -2393,7 +2399,7 @@
         <v>70</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
@@ -2411,7 +2417,7 @@
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
@@ -2467,7 +2473,7 @@
       </c>
       <c r="D52" s="29"/>
       <c r="E52" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F52" s="31"/>
       <c r="G52" s="31"/>
@@ -2483,7 +2489,7 @@
       </c>
       <c r="D53" s="29"/>
       <c r="E53" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F53" s="31"/>
       <c r="G53" s="31"/>
@@ -2499,7 +2505,7 @@
       </c>
       <c r="D54" s="29"/>
       <c r="E54" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F54" s="31"/>
       <c r="G54" s="31"/>
@@ -2515,7 +2521,7 @@
       </c>
       <c r="D55" s="29"/>
       <c r="E55" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F55" s="31"/>
       <c r="G55" s="31"/>
@@ -2531,7 +2537,7 @@
       </c>
       <c r="D56" s="29"/>
       <c r="E56" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F56" s="31"/>
       <c r="G56" s="31"/>
@@ -2549,7 +2555,7 @@
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
@@ -2565,7 +2571,7 @@
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
@@ -2581,7 +2587,7 @@
       </c>
       <c r="D59" s="20"/>
       <c r="E59" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
@@ -2597,7 +2603,7 @@
       </c>
       <c r="D60" s="20"/>
       <c r="E60" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
@@ -2613,7 +2619,7 @@
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
@@ -2629,7 +2635,7 @@
       </c>
       <c r="D62" s="20"/>
       <c r="E62" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
@@ -2645,7 +2651,7 @@
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
@@ -2663,7 +2669,7 @@
       </c>
       <c r="D64" s="29"/>
       <c r="E64" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F64" s="31"/>
       <c r="G64" s="31"/>
@@ -2679,7 +2685,7 @@
       </c>
       <c r="D65" s="29"/>
       <c r="E65" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F65" s="31"/>
       <c r="G65" s="31"/>
@@ -2694,8 +2700,8 @@
         <v>52</v>
       </c>
       <c r="D66" s="29"/>
-      <c r="E66" s="30" t="s">
-        <v>186</v>
+      <c r="E66" s="16" t="s">
+        <v>188</v>
       </c>
       <c r="F66" s="31"/>
       <c r="G66" s="31"/>
@@ -2711,7 +2717,7 @@
       </c>
       <c r="D67" s="29"/>
       <c r="E67" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -2727,7 +2733,7 @@
       </c>
       <c r="D68" s="29"/>
       <c r="E68" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F68" s="31"/>
       <c r="G68" s="31"/>
@@ -2743,7 +2749,7 @@
       </c>
       <c r="D69" s="29"/>
       <c r="E69" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F69" s="31"/>
       <c r="G69" s="31"/>
@@ -3137,50 +3143,48 @@
     <hyperlink ref="E46" r:id="rId24" display="testing456@gmail.com" xr:uid="{E5CB3F60-341B-4E47-A3EB-4D5FCC9C9862}"/>
     <hyperlink ref="E47" r:id="rId25" display="simply5@gmail.com" xr:uid="{3C9FB2CC-805B-4CA6-B509-A5420520280C}"/>
     <hyperlink ref="E39" r:id="rId26" xr:uid="{4D265B17-CB15-4B45-B46E-14845D6A16AB}"/>
-    <hyperlink ref="E57" r:id="rId27" display="simply3@gmail.com" xr:uid="{16950EB3-7FC1-4FA1-B01E-ECF2BF338688}"/>
-    <hyperlink ref="E59" r:id="rId28" display="simply2@gmail.com" xr:uid="{80D17BB9-BF25-4276-8771-34B9EAC171D1}"/>
-    <hyperlink ref="E60" r:id="rId29" display="simply2@gmail.com" xr:uid="{9ED87E8B-E71D-4753-AE8F-554EDB126343}"/>
-    <hyperlink ref="E61" r:id="rId30" display="simply1@gmail.com" xr:uid="{362206F6-430C-4F25-ADA5-73F002133C3F}"/>
-    <hyperlink ref="E63" r:id="rId31" display="simply3@gmail.com" xr:uid="{8B03735C-D05B-4520-9309-0B1AE81B68D4}"/>
-    <hyperlink ref="E62" r:id="rId32" display="simply1@gmail.com" xr:uid="{FEF0EC57-F0B8-4B34-AB58-BB30AB4B5417}"/>
-    <hyperlink ref="E54" r:id="rId33" display="simply2@gmail.com" xr:uid="{22EFF19B-656B-4B8C-8325-C23CBFFAE2CA}"/>
-    <hyperlink ref="E56" r:id="rId34" display="simply3@gmail.com" xr:uid="{FE2BB434-3B47-4CC6-AA73-8FC859713B2C}"/>
-    <hyperlink ref="E66" r:id="rId35" display="simply1@gmail.com" xr:uid="{F9FE77D0-F8A8-4FB7-BEAD-86FA6BDAB352}"/>
-    <hyperlink ref="E67" r:id="rId36" display="simply1@gmail.com" xr:uid="{7184A7BE-2587-4BF5-B3DE-3A88E27C5BDB}"/>
-    <hyperlink ref="E68" r:id="rId37" display="simply2@gmail.com" xr:uid="{37EC94D0-0EC3-4833-AF09-D714AED56A67}"/>
-    <hyperlink ref="E69" r:id="rId38" display="simply1@gmail.com" xr:uid="{7B258910-ADDA-4CE6-9CCB-9BACD22E272C}"/>
-    <hyperlink ref="E34" r:id="rId39" xr:uid="{D3DACB03-89E3-45ED-A7E9-FDEAE166A7B5}"/>
-    <hyperlink ref="E53" r:id="rId40" display="simply1@gmail.com" xr:uid="{5C4A2D47-A7C0-4FAC-BB5D-46B3A89CF3FE}"/>
-    <hyperlink ref="E55" r:id="rId41" display="simply2@gmail.com" xr:uid="{20459B7C-6DCB-4B01-BBA1-800CE957E9A4}"/>
-    <hyperlink ref="E58" r:id="rId42" display="simply3@gmail.com" xr:uid="{D08B2C40-307D-4196-8D44-3AAE4366054B}"/>
-    <hyperlink ref="E65" r:id="rId43" display="simply6@gmail.com" xr:uid="{FF234007-2A99-4193-937E-483430D8025F}"/>
-    <hyperlink ref="E36" r:id="rId44" xr:uid="{ACD5C911-DDE6-493A-BF72-10080FAB803F}"/>
-    <hyperlink ref="E15" r:id="rId45" xr:uid="{754CE5D0-FB57-435D-A72A-F5B71556605B}"/>
-    <hyperlink ref="E37" r:id="rId46" xr:uid="{E1D436D4-FF48-4A30-8BBC-80C122120C8E}"/>
-    <hyperlink ref="E50" r:id="rId47" xr:uid="{F2247F16-2565-4F01-B35A-480A808DBDF3}"/>
-    <hyperlink ref="E49" r:id="rId48" display="simply4@gmail.com" xr:uid="{89D4DA7F-893B-4AA0-8468-883415E8EE0B}"/>
-    <hyperlink ref="E35" r:id="rId49" xr:uid="{42754C57-9B3F-4988-AF3C-6DFFD113F631}"/>
-    <hyperlink ref="E24" r:id="rId50" xr:uid="{FABC0DCC-927D-4953-8CED-5FC7C1C94B7E}"/>
-    <hyperlink ref="E78" r:id="rId51" xr:uid="{520D371A-BE15-48AF-9EF5-C605DCB966AA}"/>
-    <hyperlink ref="E79" r:id="rId52" xr:uid="{2A61A99B-FECB-485A-96EF-4BE56B06F717}"/>
-    <hyperlink ref="E80" r:id="rId53" xr:uid="{3D5CD16C-B335-4097-8268-20EDB62F9003}"/>
-    <hyperlink ref="E81" r:id="rId54" xr:uid="{99830E9A-DFA6-409D-920E-D608DCD7EC83}"/>
-    <hyperlink ref="E82" r:id="rId55" xr:uid="{4D79B10F-4D29-469E-AD49-C592D75A0D48}"/>
-    <hyperlink ref="E8" r:id="rId56" xr:uid="{FB2AACCA-6426-4362-A4B0-2924FD61B151}"/>
-    <hyperlink ref="E48" r:id="rId57" display="simply4@gmail.com" xr:uid="{2A6CD140-EC42-459E-91E8-CE39A72DFCC8}"/>
-    <hyperlink ref="E84" r:id="rId58" xr:uid="{AEAB30CF-6BF7-4C89-8532-37E3DDE52411}"/>
-    <hyperlink ref="E85" r:id="rId59" xr:uid="{243345C9-8377-4F12-AF55-3B02DC8D1B8F}"/>
-    <hyperlink ref="E10" r:id="rId60" xr:uid="{74E777D6-C45F-4941-8477-D0546222FB83}"/>
-    <hyperlink ref="E83" r:id="rId61" xr:uid="{319824A4-D44E-430D-9449-E57E6752F05D}"/>
-    <hyperlink ref="E51" r:id="rId62" xr:uid="{DA82D790-63ED-410F-9F66-AE85CE900CAF}"/>
-    <hyperlink ref="E33" r:id="rId63" xr:uid="{007CA9B0-896D-408B-8B2C-38954E966151}"/>
-    <hyperlink ref="E9" r:id="rId64" display="https://simplyenergy--preprod.sandbox.lightning.force.com/a0cfc000000RcAr" xr:uid="{90A2AE7F-CDEB-4CD4-83CC-B5813E14A40D}"/>
-    <hyperlink ref="E13" r:id="rId65" xr:uid="{1418AAD4-0D4B-46B4-8A38-B301E4DB1071}"/>
-    <hyperlink ref="E64" r:id="rId66" display="simply2@gmail.com" xr:uid="{B6F39802-9D84-4735-A0C5-E351CAD1A5AC}"/>
-    <hyperlink ref="E52" r:id="rId67" display="simply1@gmail.com" xr:uid="{80712AAB-F6BD-44FF-A859-CB9F3061B388}"/>
+    <hyperlink ref="E59" r:id="rId27" xr:uid="{80D17BB9-BF25-4276-8771-34B9EAC171D1}"/>
+    <hyperlink ref="E60" r:id="rId28" xr:uid="{9ED87E8B-E71D-4753-AE8F-554EDB126343}"/>
+    <hyperlink ref="E54" r:id="rId29" xr:uid="{22EFF19B-656B-4B8C-8325-C23CBFFAE2CA}"/>
+    <hyperlink ref="E56" r:id="rId30" xr:uid="{FE2BB434-3B47-4CC6-AA73-8FC859713B2C}"/>
+    <hyperlink ref="E34" r:id="rId31" xr:uid="{D3DACB03-89E3-45ED-A7E9-FDEAE166A7B5}"/>
+    <hyperlink ref="E53" r:id="rId32" xr:uid="{5C4A2D47-A7C0-4FAC-BB5D-46B3A89CF3FE}"/>
+    <hyperlink ref="E55" r:id="rId33" xr:uid="{20459B7C-6DCB-4B01-BBA1-800CE957E9A4}"/>
+    <hyperlink ref="E36" r:id="rId34" xr:uid="{ACD5C911-DDE6-493A-BF72-10080FAB803F}"/>
+    <hyperlink ref="E15" r:id="rId35" xr:uid="{754CE5D0-FB57-435D-A72A-F5B71556605B}"/>
+    <hyperlink ref="E37" r:id="rId36" xr:uid="{E1D436D4-FF48-4A30-8BBC-80C122120C8E}"/>
+    <hyperlink ref="E50" r:id="rId37" xr:uid="{F2247F16-2565-4F01-B35A-480A808DBDF3}"/>
+    <hyperlink ref="E49" r:id="rId38" display="simply4@gmail.com" xr:uid="{89D4DA7F-893B-4AA0-8468-883415E8EE0B}"/>
+    <hyperlink ref="E35" r:id="rId39" xr:uid="{42754C57-9B3F-4988-AF3C-6DFFD113F631}"/>
+    <hyperlink ref="E24" r:id="rId40" xr:uid="{FABC0DCC-927D-4953-8CED-5FC7C1C94B7E}"/>
+    <hyperlink ref="E78" r:id="rId41" xr:uid="{520D371A-BE15-48AF-9EF5-C605DCB966AA}"/>
+    <hyperlink ref="E79" r:id="rId42" xr:uid="{2A61A99B-FECB-485A-96EF-4BE56B06F717}"/>
+    <hyperlink ref="E80" r:id="rId43" xr:uid="{3D5CD16C-B335-4097-8268-20EDB62F9003}"/>
+    <hyperlink ref="E81" r:id="rId44" xr:uid="{99830E9A-DFA6-409D-920E-D608DCD7EC83}"/>
+    <hyperlink ref="E82" r:id="rId45" xr:uid="{4D79B10F-4D29-469E-AD49-C592D75A0D48}"/>
+    <hyperlink ref="E8" r:id="rId46" xr:uid="{FB2AACCA-6426-4362-A4B0-2924FD61B151}"/>
+    <hyperlink ref="E48" r:id="rId47" display="simply4@gmail.com" xr:uid="{2A6CD140-EC42-459E-91E8-CE39A72DFCC8}"/>
+    <hyperlink ref="E84" r:id="rId48" xr:uid="{AEAB30CF-6BF7-4C89-8532-37E3DDE52411}"/>
+    <hyperlink ref="E85" r:id="rId49" xr:uid="{243345C9-8377-4F12-AF55-3B02DC8D1B8F}"/>
+    <hyperlink ref="E10" r:id="rId50" xr:uid="{74E777D6-C45F-4941-8477-D0546222FB83}"/>
+    <hyperlink ref="E83" r:id="rId51" xr:uid="{319824A4-D44E-430D-9449-E57E6752F05D}"/>
+    <hyperlink ref="E51" r:id="rId52" xr:uid="{DA82D790-63ED-410F-9F66-AE85CE900CAF}"/>
+    <hyperlink ref="E33" r:id="rId53" xr:uid="{007CA9B0-896D-408B-8B2C-38954E966151}"/>
+    <hyperlink ref="E9" r:id="rId54" xr:uid="{90A2AE7F-CDEB-4CD4-83CC-B5813E14A40D}"/>
+    <hyperlink ref="E13" r:id="rId55" xr:uid="{1418AAD4-0D4B-46B4-8A38-B301E4DB1071}"/>
+    <hyperlink ref="E52" r:id="rId56" xr:uid="{80712AAB-F6BD-44FF-A859-CB9F3061B388}"/>
+    <hyperlink ref="E61" r:id="rId57" xr:uid="{0277B7DE-173E-49E5-B013-469B58B527F0}"/>
+    <hyperlink ref="E62" r:id="rId58" xr:uid="{4F2C54DD-20ED-475A-99D2-5B5592C1E8F7}"/>
+    <hyperlink ref="E66" r:id="rId59" xr:uid="{257D4AD3-D3DA-4447-93A5-11DB48B1399E}"/>
+    <hyperlink ref="E67" r:id="rId60" xr:uid="{626C1A75-86B8-44CD-8FE3-F7CF9EDD321E}"/>
+    <hyperlink ref="E69" r:id="rId61" xr:uid="{7DADDFEA-1793-426D-85F3-EAA29E9A79B0}"/>
+    <hyperlink ref="E57" r:id="rId62" xr:uid="{BB874EF2-756E-4D00-B455-1BE5D6967288}"/>
+    <hyperlink ref="E58" r:id="rId63" xr:uid="{51757FD8-CB02-40E4-8D62-B89E52E48917}"/>
+    <hyperlink ref="E63" r:id="rId64" xr:uid="{A8081B1F-04D0-48EE-9D6A-DDC81D26DCB1}"/>
+    <hyperlink ref="E65" r:id="rId65" xr:uid="{6436D6D7-21F8-4D5D-9081-C70D87020C8E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId68"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId66"/>
 </worksheet>
 </file>
 

--- a/Test Data.xlsx
+++ b/Test Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\MyEngie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2505848-6198-4699-846A-F17BC4BCD8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BC91D8-FD85-4886-8812-659CED307370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="100" windowWidth="19190" windowHeight="10070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Browser" sheetId="9" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="192">
   <si>
     <t>Sl.No</t>
   </si>
@@ -228,9 +228,6 @@
   </si>
   <si>
     <t>Setup Direct Debit using PayPal</t>
-  </si>
-  <si>
-    <t>Pin.Customer@gmail.com</t>
   </si>
   <si>
     <t>User Name</t>
@@ -312,30 +309,6 @@
     <t>New Registartion, user suspended account user name</t>
   </si>
   <si>
-    <t>forgot.password1@gmail.com</t>
-  </si>
-  <si>
-    <t>forgot.email1@gmail.com</t>
-  </si>
-  <si>
-    <t>unlock.res@gmail.com</t>
-  </si>
-  <si>
-    <t>unlock.sme@gmail.com</t>
-  </si>
-  <si>
-    <t>wrong.otp@gmail.com</t>
-  </si>
-  <si>
-    <t>resend.otp@gmail.com</t>
-  </si>
-  <si>
-    <t>protect.comYes@gmail.com</t>
-  </si>
-  <si>
-    <t>wrong.pin@gmail.com</t>
-  </si>
-  <si>
     <t>new.res@gmail.com</t>
   </si>
   <si>
@@ -375,117 +348,33 @@
     <t>newres.proYesComsYes@gmail.com</t>
   </si>
   <si>
-    <t>newres.resetmobile@gmail.com</t>
-  </si>
-  <si>
-    <t>business@gmail.com</t>
-  </si>
-  <si>
-    <t>residential@gmail.com</t>
-  </si>
-  <si>
-    <t>payment.extension@gmail.com</t>
-  </si>
-  <si>
     <t>Account balance validation</t>
   </si>
   <si>
     <t>Existing Csutomer Become Protected Customer</t>
   </si>
   <si>
-    <t>22-06-1964</t>
-  </si>
-  <si>
-    <t>08-10-1959</t>
-  </si>
-  <si>
-    <t>07-10-1969</t>
-  </si>
-  <si>
-    <t>24-08-1962</t>
-  </si>
-  <si>
-    <t>22-05-1985</t>
-  </si>
-  <si>
-    <t>11-10-1969</t>
-  </si>
-  <si>
-    <t>08-12-1997</t>
-  </si>
-  <si>
-    <t>28-07-1985</t>
-  </si>
-  <si>
-    <t>24-07-1959</t>
-  </si>
-  <si>
-    <t>29-11-1994</t>
-  </si>
-  <si>
-    <t>25-08-1993</t>
-  </si>
-  <si>
-    <t>17-05-1999</t>
-  </si>
-  <si>
-    <t>15-03-1952</t>
-  </si>
-  <si>
-    <t>21-08-1961</t>
-  </si>
-  <si>
-    <t>28-04-1957</t>
-  </si>
-  <si>
-    <t>14-08-1963</t>
-  </si>
-  <si>
-    <t>26-06-1932</t>
-  </si>
-  <si>
-    <t>10-12-1960</t>
-  </si>
-  <si>
     <t>harsha@noesyssoftware.com</t>
   </si>
   <si>
-    <t>03-06-1980</t>
-  </si>
-  <si>
     <t>Submitt the enquiry form for an Linked account &amp; verify the my enquires</t>
   </si>
   <si>
     <t>Update Mobile Number</t>
   </si>
   <si>
-    <t>simply5@gmail.com</t>
-  </si>
-  <si>
-    <t>22-05-1981</t>
-  </si>
-  <si>
     <t>EditConcession@gmail.com</t>
   </si>
   <si>
-    <t>09-11-1973</t>
-  </si>
-  <si>
     <t>Unable to Link Secondary Contact</t>
   </si>
   <si>
-    <t>15-09-1979</t>
-  </si>
-  <si>
     <t>The account cannot be linked as the primary contact details do not match the linking account customer</t>
   </si>
   <si>
     <t>Business Customer Link Business customer Account &amp; Residentail Customer Account</t>
   </si>
   <si>
-    <t>Residential Customer Link Link Residentail customer  Account (Able to Link Primary Contact &amp; signatrory is enabled) &amp; Business Account Customer</t>
-  </si>
-  <si>
     <t>CUID_2</t>
   </si>
   <si>
@@ -495,9 +384,6 @@
     <t>ABN/DOB_2</t>
   </si>
   <si>
-    <t>25-10-1982</t>
-  </si>
-  <si>
     <t>New Registartion Without Email address,use '. ' symbol in  username, update mailing address and make an enquiry with attachment and check SF for all</t>
   </si>
   <si>
@@ -522,21 +408,6 @@
     <t>Registartion Without Email--&gt;use '_ ' symbol in username, update mailing address and make an enquiry with attachment and check SF for all</t>
   </si>
   <si>
-    <t>30-09-1958</t>
-  </si>
-  <si>
-    <t>17-05-1977</t>
-  </si>
-  <si>
-    <t>29-10-1962</t>
-  </si>
-  <si>
-    <t>18-06-1992</t>
-  </si>
-  <si>
-    <t>04-08-1954</t>
-  </si>
-  <si>
     <t>register-MFA@gmail.com</t>
   </si>
   <si>
@@ -585,41 +456,173 @@
     <t>Add_Fuel_WA_Customer</t>
   </si>
   <si>
-    <t>02-02-1992</t>
-  </si>
-  <si>
-    <t>ramyacgowda187@gmail.com</t>
-  </si>
-  <si>
-    <t>18-01-1947</t>
-  </si>
-  <si>
-    <t>21-04-1992</t>
-  </si>
-  <si>
-    <t>testing123@gmail.com</t>
-  </si>
-  <si>
-    <t>testing234@gmail.com</t>
-  </si>
-  <si>
-    <t>ramya@noesyssoftware.com</t>
-  </si>
-  <si>
-    <t>muttu@gmail.com</t>
-  </si>
-  <si>
-    <t>muttu1@gmail.com</t>
-  </si>
-  <si>
-    <t>muttu2@gmail.com</t>
+    <t>forgot.password@gmail.com</t>
+  </si>
+  <si>
+    <t>Pin.Customer1@gmail.com</t>
+  </si>
+  <si>
+    <t>forgot.email@gmail.com</t>
+  </si>
+  <si>
+    <t>ramyakgowda678@gmail.com</t>
+  </si>
+  <si>
+    <t>unlock.residential@gmail.com</t>
+  </si>
+  <si>
+    <t>unlock.sme1@gmail.com</t>
+  </si>
+  <si>
+    <t>wrong.otp1@gmail.com</t>
+  </si>
+  <si>
+    <t>80072939005</t>
+  </si>
+  <si>
+    <t>71689390761</t>
+  </si>
+  <si>
+    <t>14-05-1993</t>
+  </si>
+  <si>
+    <t>23-04-1983</t>
+  </si>
+  <si>
+    <t>29-10-1992</t>
+  </si>
+  <si>
+    <t>07-11-1994</t>
+  </si>
+  <si>
+    <t>23-05-1982</t>
+  </si>
+  <si>
+    <t>22-07-1985</t>
+  </si>
+  <si>
+    <t>resend.otp1@gmail.com</t>
+  </si>
+  <si>
+    <t>protect.comYes1@gmail.com</t>
+  </si>
+  <si>
+    <t>02-11-1957</t>
+  </si>
+  <si>
+    <t>05-07-1964</t>
+  </si>
+  <si>
+    <t>wrongpin.thrice@gmail.com</t>
+  </si>
+  <si>
+    <t>30-11-1984</t>
+  </si>
+  <si>
+    <t>soujanya@noesyssoftware.com</t>
+  </si>
+  <si>
+    <t>26-04-1981</t>
+  </si>
+  <si>
+    <t>11-02-1994</t>
+  </si>
+  <si>
+    <t>24-08-1964</t>
+  </si>
+  <si>
+    <t>08-10-1981</t>
+  </si>
+  <si>
+    <t>27-03-1936</t>
+  </si>
+  <si>
+    <t>17-10-1984</t>
+  </si>
+  <si>
+    <t>27-12-1956</t>
+  </si>
+  <si>
+    <t>29-08-1983</t>
+  </si>
+  <si>
+    <t>36092186475</t>
+  </si>
+  <si>
+    <t>52665339766</t>
+  </si>
+  <si>
+    <t>85836958201</t>
+  </si>
+  <si>
+    <t>29-08-1974</t>
+  </si>
+  <si>
+    <t>23-03-1971</t>
+  </si>
+  <si>
+    <t>04-12-1988</t>
+  </si>
+  <si>
+    <t>31-01-1981</t>
+  </si>
+  <si>
+    <t>17-06-1933</t>
+  </si>
+  <si>
+    <t>27-02-1960</t>
+  </si>
+  <si>
+    <t>13-02-1972</t>
+  </si>
+  <si>
+    <t>07-09-1988</t>
+  </si>
+  <si>
+    <t>24-10-1997</t>
+  </si>
+  <si>
+    <t>Residential Customer Link Residentail customer  Account (Able to Link Primary Contact &amp; signatrory is enabled) &amp; Business Account Customer</t>
+  </si>
+  <si>
+    <t>business1@gmail.com</t>
+  </si>
+  <si>
+    <t>18-11-1966</t>
+  </si>
+  <si>
+    <t>residential1@gmail.com</t>
+  </si>
+  <si>
+    <t>27-07-1998</t>
+  </si>
+  <si>
+    <t>payment.extension1@gmail.com</t>
+  </si>
+  <si>
+    <t>test_test123@gmail.com</t>
+  </si>
+  <si>
+    <t>31-08-1996</t>
+  </si>
+  <si>
+    <t>28-09-1993</t>
+  </si>
+  <si>
+    <t>test_test234@gmail.com</t>
+  </si>
+  <si>
+    <t>03-07-1990</t>
+  </si>
+  <si>
+    <t>test_test678@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -681,20 +684,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,6 +712,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -785,7 +793,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -859,9 +867,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -874,15 +879,9 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -910,32 +909,74 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -952,24 +993,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1260,13 +1283,13 @@
     <col min="2" max="2" width="20.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="85.26953125" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.81640625" style="10" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="34.54296875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="36.6328125" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.453125" style="3" customWidth="1"/>
     <col min="7" max="7" width="12.90625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.7265625" style="41" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" style="38" customWidth="1"/>
     <col min="9" max="9" width="10.6328125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="6.81640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.08984375" style="41" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" style="38" customWidth="1"/>
     <col min="12" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
@@ -1284,924 +1307,912 @@
         <v>61</v>
       </c>
       <c r="E1" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="33" t="s">
-        <v>67</v>
-      </c>
       <c r="I1" s="18" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>150</v>
+        <v>112</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="42" t="s">
-        <v>154</v>
+      <c r="C2" s="43" t="s">
+        <v>116</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>90</v>
+        <v>69</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>138</v>
       </c>
       <c r="F2" s="14">
-        <v>33770499</v>
+        <v>53560867</v>
       </c>
       <c r="G2" s="14">
-        <v>6014</v>
-      </c>
-      <c r="H2" s="34">
-        <v>23067730578</v>
+        <v>4565</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="56"/>
+      <c r="B3" s="67"/>
       <c r="C3" s="15" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>139</v>
       </c>
       <c r="F3" s="14">
-        <v>26880916</v>
+        <v>35599352</v>
       </c>
       <c r="G3" s="14">
-        <v>6107</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>117</v>
+        <v>6163</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="56"/>
+      <c r="B4" s="67"/>
       <c r="C4" s="15" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>90</v>
+        <v>69</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>138</v>
       </c>
       <c r="F4" s="14">
-        <v>33770499</v>
+        <v>53560867</v>
       </c>
       <c r="G4" s="14">
-        <v>6014</v>
-      </c>
-      <c r="H4" s="34">
-        <v>23067730578</v>
+        <v>4565</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="56"/>
+      <c r="B5" s="67"/>
       <c r="C5" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>91</v>
+        <v>69</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>140</v>
       </c>
       <c r="F5" s="14">
-        <v>28324293</v>
+        <v>72016308</v>
       </c>
       <c r="G5" s="14">
-        <v>6059</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>118</v>
+        <v>6169</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="56"/>
+      <c r="B6" s="67"/>
       <c r="C6" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>139</v>
       </c>
       <c r="F6" s="14">
-        <v>26880916</v>
+        <v>35599352</v>
       </c>
       <c r="G6" s="14">
-        <v>6107</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>117</v>
+        <v>6163</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="56"/>
+      <c r="B7" s="67"/>
       <c r="C7" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>91</v>
+        <v>69</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>140</v>
       </c>
       <c r="F7" s="14">
-        <v>28324293</v>
+        <v>72016308</v>
       </c>
       <c r="G7" s="14">
-        <v>6059</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>118</v>
+        <v>6169</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="56"/>
+      <c r="B8" s="67"/>
       <c r="C8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>182</v>
+        <v>69</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>141</v>
       </c>
       <c r="F8" s="14">
-        <v>40426020</v>
+        <v>49871769</v>
       </c>
       <c r="G8" s="14">
-        <v>2010</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>181</v>
+        <v>5069</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="56"/>
+      <c r="B9" s="67"/>
       <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>187</v>
+        <v>69</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>104</v>
       </c>
       <c r="F9" s="14">
-        <v>30061825</v>
+        <v>66793635</v>
       </c>
       <c r="G9" s="14">
-        <v>6156</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>134</v>
+        <v>5108</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="56"/>
+      <c r="B10" s="67"/>
       <c r="C10" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>92</v>
+        <v>69</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>142</v>
       </c>
       <c r="F10" s="14">
-        <v>32048517</v>
+        <v>21870441</v>
       </c>
       <c r="G10" s="14">
-        <v>6169</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>119</v>
+        <v>5114</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="56"/>
-      <c r="C11" s="15" t="s">
-        <v>82</v>
+      <c r="B11" s="67"/>
+      <c r="C11" s="43" t="s">
+        <v>81</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>93</v>
+        <v>69</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>143</v>
       </c>
       <c r="F11" s="14">
-        <v>35169445</v>
+        <v>68815195</v>
       </c>
       <c r="G11" s="14">
-        <v>6052</v>
-      </c>
-      <c r="H11" s="34">
-        <v>70970907504</v>
+        <v>3121</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="56"/>
+      <c r="B12" s="67"/>
       <c r="C12" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>94</v>
+        <v>69</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>144</v>
       </c>
       <c r="F12" s="14">
-        <v>27890673</v>
+        <v>66085766</v>
       </c>
       <c r="G12" s="14">
-        <v>6163</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>120</v>
+        <v>3189</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="56"/>
+      <c r="B13" s="67"/>
       <c r="C13" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>95</v>
+        <v>69</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>153</v>
       </c>
       <c r="F13" s="14">
-        <v>31389092</v>
+        <v>32088318</v>
       </c>
       <c r="G13" s="14">
-        <v>4035</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>121</v>
+        <v>5045</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="56"/>
+      <c r="B14" s="67"/>
       <c r="C14" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>96</v>
+        <v>69</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>154</v>
       </c>
       <c r="F14" s="14">
-        <v>22883457</v>
+        <v>66769237</v>
       </c>
       <c r="G14" s="14">
-        <v>4510</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>122</v>
+        <v>5118</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="57"/>
+      <c r="B15" s="68"/>
       <c r="C15" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>139</v>
+        <v>69</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>157</v>
       </c>
       <c r="F15" s="14">
-        <v>49441751</v>
+        <v>66711310</v>
       </c>
       <c r="G15" s="14">
-        <v>4305</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>123</v>
+        <v>5608</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="60" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>98</v>
+        <v>69</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>89</v>
       </c>
       <c r="F16" s="14">
-        <v>37965339</v>
+        <v>66689744</v>
       </c>
       <c r="G16" s="14">
-        <v>4209</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>124</v>
+        <v>5108</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="59"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>99</v>
+        <v>69</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>90</v>
       </c>
       <c r="F17" s="14">
-        <v>35228221</v>
+        <v>66834130</v>
       </c>
       <c r="G17" s="14">
-        <v>6122</v>
-      </c>
-      <c r="H17" s="34">
-        <v>95624433674</v>
+        <v>3807</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="59"/>
+      <c r="B18" s="61"/>
       <c r="C18" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>100</v>
+        <v>69</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>91</v>
       </c>
       <c r="F18" s="14">
-        <v>54597815</v>
+        <v>29153872</v>
       </c>
       <c r="G18" s="14">
-        <v>5162</v>
-      </c>
-      <c r="H18" s="34" t="s">
-        <v>184</v>
+        <v>5290</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="61"/>
       <c r="C19" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>101</v>
+        <v>69</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>92</v>
       </c>
       <c r="F19" s="14">
-        <v>33831960</v>
+        <v>17712715</v>
       </c>
       <c r="G19" s="14">
-        <v>4301</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>136</v>
+        <v>5074</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="49" t="s">
-        <v>152</v>
+      <c r="B20" s="61"/>
+      <c r="C20" s="43" t="s">
+        <v>114</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>103</v>
+        <v>69</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>94</v>
       </c>
       <c r="F20" s="21">
-        <v>30460919</v>
+        <v>58098612</v>
       </c>
       <c r="G20" s="14">
-        <v>3021</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>183</v>
+        <v>5163</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="59"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>103</v>
+        <v>86</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>94</v>
       </c>
       <c r="F21" s="14">
-        <v>31766412</v>
+        <v>8278249</v>
       </c>
       <c r="G21" s="14">
-        <v>6210</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>125</v>
+        <v>5031</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="59"/>
+      <c r="B22" s="61"/>
       <c r="C22" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>135</v>
+        <v>69</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>159</v>
       </c>
       <c r="F22" s="14">
-        <v>30009843</v>
+        <v>16474611</v>
       </c>
       <c r="G22" s="14">
-        <v>6061</v>
-      </c>
-      <c r="H22" s="34" t="s">
-        <v>126</v>
+        <v>5091</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="59"/>
+      <c r="B23" s="61"/>
       <c r="C23" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>135</v>
+        <v>69</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>159</v>
       </c>
       <c r="F23" s="14">
-        <v>49579601</v>
+        <v>7017241</v>
       </c>
       <c r="G23" s="14">
-        <v>6152</v>
-      </c>
-      <c r="H23" s="34" t="s">
-        <v>127</v>
+        <v>5019</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="59"/>
+      <c r="B24" s="61"/>
       <c r="C24" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>97</v>
+        <v>86</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>157</v>
       </c>
       <c r="F24" s="14">
-        <v>37965339</v>
+        <v>66080207</v>
       </c>
       <c r="G24" s="14">
-        <v>4209</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>124</v>
+        <v>5095</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="60"/>
+      <c r="B25" s="62"/>
       <c r="C25" s="11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="12">
-        <v>47903100</v>
-      </c>
-      <c r="G25" s="12">
-        <v>6061</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>128</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="63" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>109</v>
+        <v>69</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>27608078</v>
+        <v>1749592</v>
       </c>
       <c r="G26" s="14">
-        <v>6210</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>129</v>
+        <v>5018</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="53"/>
+      <c r="B27" s="64"/>
       <c r="C27" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>106</v>
+        <v>69</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>97</v>
       </c>
       <c r="F27" s="14">
-        <v>27977471</v>
+        <v>68814437</v>
       </c>
       <c r="G27" s="14">
-        <v>6233</v>
-      </c>
-      <c r="H27" s="34" t="s">
-        <v>130</v>
+        <v>5109</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="53"/>
+      <c r="B28" s="64"/>
       <c r="C28" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>107</v>
+        <v>69</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>98</v>
       </c>
       <c r="F28" s="14">
-        <v>38454272</v>
+        <v>66782593</v>
       </c>
       <c r="G28" s="14">
-        <v>2031</v>
-      </c>
-      <c r="H28" s="34">
-        <v>97242275785</v>
+        <v>3198</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="53"/>
+      <c r="B29" s="64"/>
       <c r="C29" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>108</v>
+        <v>69</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>99</v>
       </c>
       <c r="F29" s="14">
-        <v>34699865</v>
+        <v>26405048</v>
       </c>
       <c r="G29" s="14">
-        <v>2780</v>
-      </c>
-      <c r="H29" s="34">
-        <v>50613003044</v>
+        <v>3224</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="53"/>
+      <c r="B30" s="64"/>
       <c r="C30" s="15" t="s">
         <v>25</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>110</v>
+        <v>69</v>
+      </c>
+      <c r="E30" s="45" t="s">
+        <v>101</v>
       </c>
       <c r="F30" s="14">
-        <v>26988412</v>
+        <v>30702776</v>
       </c>
       <c r="G30" s="14">
-        <v>6233</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>131</v>
+        <v>5113</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="54"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>111</v>
+        <v>69</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>159</v>
       </c>
       <c r="F31" s="14">
-        <v>49465598</v>
+        <v>40434027</v>
       </c>
       <c r="G31" s="14">
-        <v>4020</v>
-      </c>
-      <c r="H31" s="34" t="s">
-        <v>132</v>
+        <v>5046</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="60" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>139</v>
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
-      <c r="H32" s="34"/>
+      <c r="H32" s="31"/>
     </row>
     <row r="33" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="59"/>
+      <c r="B33" s="61"/>
       <c r="C33" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>182</v>
+        <v>69</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>141</v>
       </c>
       <c r="F33" s="14">
-        <v>27608078</v>
+        <v>1749592</v>
       </c>
       <c r="G33" s="14">
-        <v>6210</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>129</v>
+        <v>5018</v>
+      </c>
+      <c r="H33" s="47" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="59"/>
+      <c r="B34" s="61"/>
       <c r="C34" s="15" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F34" s="32">
-        <v>37571270</v>
-      </c>
-      <c r="G34" s="32">
-        <v>6155</v>
-      </c>
-      <c r="H34" s="32">
-        <v>27892688791</v>
+        <v>69</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" s="48">
+        <v>63732565</v>
+      </c>
+      <c r="G34" s="48">
+        <v>6000</v>
+      </c>
+      <c r="H34" s="49">
+        <v>32589465297</v>
       </c>
       <c r="I34" s="12">
-        <v>28700473</v>
-      </c>
-      <c r="J34" s="3">
-        <v>6530</v>
-      </c>
-      <c r="K34" s="34" t="s">
-        <v>151</v>
+        <v>32088419</v>
+      </c>
+      <c r="J34" s="5">
+        <v>2023</v>
+      </c>
+      <c r="K34" s="31" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="60"/>
+      <c r="B35" s="62"/>
       <c r="C35" s="15" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" s="31">
-        <v>26906914</v>
-      </c>
-      <c r="G35" s="31">
-        <v>6162</v>
-      </c>
-      <c r="H35" s="36" t="s">
-        <v>133</v>
+        <v>69</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="F35" s="29">
+        <v>49882627</v>
+      </c>
+      <c r="G35" s="29">
+        <v>2759</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>182</v>
       </c>
       <c r="I35" s="12">
-        <v>44736716</v>
-      </c>
-      <c r="J35" s="3">
-        <v>6050</v>
+        <v>66834130</v>
+      </c>
+      <c r="J35" s="5">
+        <v>3807</v>
       </c>
       <c r="K35" s="12">
-        <v>85105745695</v>
+        <v>36092186475</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="58" t="s">
+      <c r="B36" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="43" t="s">
-        <v>153</v>
+      <c r="C36" s="39" t="s">
+        <v>115</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" s="14">
-        <v>12074268</v>
-      </c>
-      <c r="G36" s="14">
-        <v>4069</v>
-      </c>
-      <c r="H36" s="34" t="s">
-        <v>133</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="31"/>
     </row>
     <row r="37" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="59"/>
-      <c r="C37" s="26" t="s">
+      <c r="B37" s="61"/>
+      <c r="C37" s="25" t="s">
         <v>33</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>113</v>
+        <v>69</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>183</v>
       </c>
       <c r="F37" s="14"/>
       <c r="G37" s="14"/>
-      <c r="H37" s="34"/>
+      <c r="H37" s="31"/>
     </row>
     <row r="38" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="26" t="s">
+      <c r="B38" s="62"/>
+      <c r="C38" s="25" t="s">
         <v>59</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>113</v>
+        <v>69</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>183</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
-      <c r="H38" s="34"/>
+      <c r="H38" s="31"/>
     </row>
     <row r="39" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
@@ -2210,44 +2221,38 @@
       <c r="B39" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="25" t="s">
         <v>60</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="F39" s="14">
-        <v>26906634</v>
-      </c>
-      <c r="G39" s="14">
-        <v>6164</v>
-      </c>
-      <c r="H39" s="34" t="s">
-        <v>142</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="31"/>
     </row>
     <row r="40" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="26" t="s">
         <v>68</v>
       </c>
+      <c r="C40" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="D40" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>114</v>
+        <v>69</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
-      <c r="H40" s="34"/>
+      <c r="H40" s="31"/>
     </row>
     <row r="41" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
@@ -2256,520 +2261,526 @@
       <c r="B41" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="26" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>114</v>
+        <v>69</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>185</v>
       </c>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
-      <c r="H41" s="34"/>
+      <c r="H41" s="31"/>
     </row>
     <row r="42" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="58" t="s">
+      <c r="B42" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>185</v>
+        <v>69</v>
+      </c>
+      <c r="E42" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="F42" s="14">
-        <v>21696233</v>
-      </c>
-      <c r="G42" s="14"/>
-      <c r="H42" s="34"/>
+        <v>49919324</v>
+      </c>
+      <c r="G42" s="14">
+        <v>2200</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="43" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="26" t="s">
+      <c r="B43" s="61"/>
+      <c r="C43" s="25" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>185</v>
+        <v>69</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="F43" s="14"/>
       <c r="G43" s="14"/>
-      <c r="H43" s="34"/>
+      <c r="H43" s="31"/>
     </row>
     <row r="44" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="59"/>
-      <c r="C44" s="26" t="s">
+      <c r="B44" s="61"/>
+      <c r="C44" s="25" t="s">
         <v>38</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>186</v>
+        <v>69</v>
+      </c>
+      <c r="E44" s="45" t="s">
+        <v>189</v>
       </c>
       <c r="F44" s="14">
-        <v>21731062</v>
-      </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="34"/>
+        <v>69670931</v>
+      </c>
+      <c r="G44" s="14">
+        <v>2209</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="45" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="26" t="s">
+      <c r="B45" s="62"/>
+      <c r="C45" s="25" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>186</v>
+        <v>69</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>189</v>
       </c>
       <c r="F45" s="14"/>
       <c r="G45" s="14"/>
-      <c r="H45" s="34"/>
+      <c r="H45" s="31"/>
     </row>
     <row r="46" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="58" t="s">
+      <c r="B46" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="25" t="s">
         <v>40</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="F46" s="14">
-        <v>30460919</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="F46" s="14"/>
       <c r="G46" s="14"/>
-      <c r="H46" s="34"/>
+      <c r="H46" s="31"/>
     </row>
     <row r="47" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="60"/>
-      <c r="C47" s="26" t="s">
+      <c r="B47" s="62"/>
+      <c r="C47" s="25" t="s">
         <v>41</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>186</v>
+        <v>69</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>189</v>
       </c>
       <c r="F47" s="14"/>
       <c r="G47" s="14"/>
-      <c r="H47" s="34"/>
+      <c r="H47" s="31"/>
     </row>
     <row r="48" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="17"/>
-      <c r="C48" s="26" t="s">
-        <v>115</v>
+      <c r="C48" s="25" t="s">
+        <v>102</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>185</v>
+        <v>69</v>
+      </c>
+      <c r="E48" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
-      <c r="H48" s="34"/>
+      <c r="H48" s="31"/>
     </row>
     <row r="49" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="25" t="s">
         <v>30</v>
       </c>
       <c r="D49" s="20"/>
-      <c r="E49" s="16" t="s">
-        <v>185</v>
+      <c r="E49" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
-      <c r="H49" s="34"/>
+      <c r="H49" s="31"/>
     </row>
     <row r="50" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="60"/>
-      <c r="C50" s="26" t="s">
+      <c r="B50" s="62"/>
+      <c r="C50" s="25" t="s">
         <v>31</v>
       </c>
       <c r="D50" s="20"/>
       <c r="E50" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="F50" s="14">
-        <v>21916337</v>
-      </c>
-      <c r="G50" s="14">
-        <v>2488</v>
-      </c>
-      <c r="H50" s="34" t="s">
-        <v>140</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="31"/>
     </row>
     <row r="51" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="9"/>
-      <c r="C51" s="26" t="s">
-        <v>116</v>
+      <c r="C51" s="25" t="s">
+        <v>103</v>
       </c>
       <c r="D51" s="20"/>
-      <c r="E51" s="16" t="s">
-        <v>113</v>
+      <c r="E51" s="45" t="s">
+        <v>183</v>
       </c>
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
-      <c r="H51" s="34"/>
+      <c r="H51" s="31"/>
     </row>
     <row r="52" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="58" t="s">
+      <c r="B52" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D52" s="29"/>
-      <c r="E52" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="36"/>
+      <c r="C52" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="28"/>
+      <c r="E52" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="33"/>
     </row>
     <row r="53" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="59"/>
-      <c r="C53" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D53" s="29"/>
-      <c r="E53" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="36"/>
+      <c r="B53" s="61"/>
+      <c r="C53" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53" s="28"/>
+      <c r="E53" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="33"/>
     </row>
     <row r="54" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="59"/>
-      <c r="C54" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D54" s="29"/>
-      <c r="E54" s="16" t="s">
+      <c r="B54" s="61"/>
+      <c r="C54" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="28"/>
+      <c r="E54" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="36"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="33"/>
     </row>
     <row r="55" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="59"/>
-      <c r="C55" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" s="29"/>
-      <c r="E55" s="16" t="s">
+      <c r="B55" s="61"/>
+      <c r="C55" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="28"/>
+      <c r="E55" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="36"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="33"/>
     </row>
     <row r="56" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="60"/>
-      <c r="C56" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D56" s="29"/>
+      <c r="B56" s="62"/>
+      <c r="C56" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" s="28"/>
       <c r="E56" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="F56" s="29">
+        <v>66826385</v>
+      </c>
+      <c r="G56" s="29">
+        <v>2261</v>
+      </c>
+      <c r="H56" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="36"/>
     </row>
     <row r="57" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="58" t="s">
+      <c r="B57" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="C57" s="25" t="s">
         <v>43</v>
       </c>
       <c r="D57" s="20"/>
       <c r="E57" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
-      <c r="H57" s="34"/>
+      <c r="H57" s="31"/>
     </row>
     <row r="58" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="59"/>
-      <c r="C58" s="26" t="s">
+      <c r="B58" s="61"/>
+      <c r="C58" s="25" t="s">
         <v>44</v>
       </c>
       <c r="D58" s="20"/>
       <c r="E58" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
-      <c r="H58" s="34"/>
+      <c r="H58" s="31"/>
     </row>
     <row r="59" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="59"/>
-      <c r="C59" s="26" t="s">
+      <c r="B59" s="61"/>
+      <c r="C59" s="25" t="s">
         <v>45</v>
       </c>
       <c r="D59" s="20"/>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="45" t="s">
         <v>189</v>
       </c>
       <c r="F59" s="14"/>
       <c r="G59" s="14"/>
-      <c r="H59" s="34"/>
+      <c r="H59" s="31"/>
     </row>
     <row r="60" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="59"/>
-      <c r="C60" s="26" t="s">
+      <c r="B60" s="61"/>
+      <c r="C60" s="25" t="s">
         <v>46</v>
       </c>
       <c r="D60" s="20"/>
-      <c r="E60" s="16" t="s">
+      <c r="E60" s="45" t="s">
         <v>189</v>
       </c>
       <c r="F60" s="14"/>
       <c r="G60" s="14"/>
-      <c r="H60" s="34"/>
+      <c r="H60" s="31"/>
     </row>
     <row r="61" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="59"/>
-      <c r="C61" s="26" t="s">
+      <c r="B61" s="61"/>
+      <c r="C61" s="25" t="s">
         <v>47</v>
       </c>
       <c r="D61" s="20"/>
-      <c r="E61" s="16" t="s">
-        <v>188</v>
+      <c r="E61" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="F61" s="14"/>
       <c r="G61" s="14"/>
-      <c r="H61" s="34"/>
+      <c r="H61" s="31"/>
     </row>
     <row r="62" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="59"/>
-      <c r="C62" s="26" t="s">
+      <c r="B62" s="61"/>
+      <c r="C62" s="25" t="s">
         <v>48</v>
       </c>
       <c r="D62" s="20"/>
-      <c r="E62" s="16" t="s">
-        <v>188</v>
+      <c r="E62" s="45" t="s">
+        <v>186</v>
       </c>
       <c r="F62" s="14"/>
       <c r="G62" s="14"/>
-      <c r="H62" s="34"/>
+      <c r="H62" s="31"/>
     </row>
     <row r="63" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="60"/>
-      <c r="C63" s="26" t="s">
+      <c r="B63" s="62"/>
+      <c r="C63" s="25" t="s">
         <v>62</v>
       </c>
       <c r="D63" s="20"/>
       <c r="E63" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="14"/>
-      <c r="H63" s="34"/>
+      <c r="H63" s="31"/>
     </row>
     <row r="64" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="58" t="s">
+      <c r="B64" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="C64" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D64" s="29"/>
-      <c r="E64" s="16" t="s">
+      <c r="C64" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" s="28"/>
+      <c r="E64" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="36"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="33"/>
     </row>
     <row r="65" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="59"/>
-      <c r="C65" s="28" t="s">
+      <c r="B65" s="61"/>
+      <c r="C65" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D65" s="29"/>
-      <c r="E65" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="36"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="33"/>
     </row>
     <row r="66" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="59"/>
-      <c r="C66" s="28" t="s">
+      <c r="B66" s="61"/>
+      <c r="C66" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D66" s="29"/>
-      <c r="E66" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="36"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="33"/>
     </row>
     <row r="67" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="59"/>
-      <c r="C67" s="28" t="s">
+      <c r="B67" s="61"/>
+      <c r="C67" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D67" s="29"/>
-      <c r="E67" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="36"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="33"/>
     </row>
     <row r="68" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="59"/>
-      <c r="C68" s="28" t="s">
+      <c r="B68" s="61"/>
+      <c r="C68" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D68" s="29"/>
-      <c r="E68" s="16" t="s">
+      <c r="D68" s="28"/>
+      <c r="E68" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="36"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="33"/>
     </row>
     <row r="69" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="59"/>
-      <c r="C69" s="28" t="s">
+      <c r="B69" s="61"/>
+      <c r="C69" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="29"/>
-      <c r="E69" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="36"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="33"/>
     </row>
     <row r="70" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="60"/>
-      <c r="C70" s="28" t="s">
+      <c r="B70" s="62"/>
+      <c r="C70" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D70" s="29"/>
-      <c r="E70" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="36"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="33"/>
     </row>
     <row r="71" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
@@ -2777,13 +2788,15 @@
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D71" s="37"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
-      <c r="H71" s="39"/>
+        <v>105</v>
+      </c>
+      <c r="D71" s="34"/>
+      <c r="E71" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="F71" s="35"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="36"/>
     </row>
     <row r="72" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
@@ -2791,19 +2804,21 @@
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="14" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="D72" s="20"/>
-      <c r="E72" s="14"/>
+      <c r="E72" s="45" t="s">
+        <v>183</v>
+      </c>
       <c r="F72" s="14"/>
       <c r="G72" s="14"/>
-      <c r="H72" s="34"/>
+      <c r="H72" s="31"/>
     </row>
     <row r="73" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="58" t="s">
+      <c r="B73" s="60" t="s">
         <v>49</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -2813,13 +2828,13 @@
       <c r="E73" s="6"/>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="40"/>
+      <c r="H73" s="37"/>
     </row>
     <row r="74" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="59"/>
+      <c r="B74" s="61"/>
       <c r="C74" s="8" t="s">
         <v>4</v>
       </c>
@@ -2827,13 +2842,13 @@
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="40"/>
+      <c r="H74" s="37"/>
     </row>
     <row r="75" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="60"/>
+      <c r="B75" s="62"/>
       <c r="C75" s="8" t="s">
         <v>5</v>
       </c>
@@ -2841,266 +2856,275 @@
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="40"/>
+      <c r="H75" s="37"/>
     </row>
     <row r="76" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="61" t="s">
+      <c r="B76" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="D76" s="29"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="31">
-        <v>27505876</v>
-      </c>
-      <c r="G76" s="31">
-        <v>6060</v>
-      </c>
-      <c r="H76" s="36" t="s">
-        <v>144</v>
+      <c r="C76" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="28"/>
+      <c r="E76" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="F76" s="29">
+        <v>58030500</v>
+      </c>
+      <c r="G76" s="29">
+        <v>2119</v>
+      </c>
+      <c r="H76" s="51" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="63"/>
-      <c r="C77" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="E77" s="45"/>
-      <c r="F77" s="46">
-        <v>21916337</v>
-      </c>
-      <c r="G77" s="46">
-        <v>2488</v>
-      </c>
-      <c r="H77" s="47" t="s">
-        <v>140</v>
+      <c r="B77" s="59"/>
+      <c r="C77" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="E77" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="F77" s="41">
+        <v>66792323</v>
+      </c>
+      <c r="G77" s="41">
+        <v>2763</v>
+      </c>
+      <c r="H77" s="52" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="61" t="s">
-        <v>167</v>
-      </c>
-      <c r="C78" s="48" t="s">
-        <v>155</v>
+      <c r="B78" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C78" s="42" t="s">
+        <v>117</v>
       </c>
       <c r="D78" s="20"/>
-      <c r="E78" s="16" t="s">
-        <v>165</v>
+      <c r="E78" s="45" t="s">
+        <v>122</v>
       </c>
       <c r="F78" s="14">
-        <v>31364813</v>
+        <v>11133786</v>
       </c>
       <c r="G78" s="14">
-        <v>2213</v>
-      </c>
-      <c r="H78" s="34" t="s">
-        <v>160</v>
+        <v>5290</v>
+      </c>
+      <c r="H78" s="47" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="62"/>
+      <c r="B79" s="58"/>
       <c r="C79" s="14" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="D79" s="20"/>
-      <c r="E79" s="16" t="s">
-        <v>166</v>
+      <c r="E79" s="45" t="s">
+        <v>123</v>
       </c>
       <c r="F79" s="14">
-        <v>54947955</v>
+        <v>6974094</v>
       </c>
       <c r="G79" s="14">
-        <v>2519</v>
-      </c>
-      <c r="H79" s="34" t="s">
-        <v>161</v>
+        <v>5041</v>
+      </c>
+      <c r="H79" s="47" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="62"/>
+      <c r="B80" s="58"/>
       <c r="C80" s="19" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="D80" s="20"/>
-      <c r="E80" s="16" t="s">
-        <v>168</v>
+      <c r="E80" s="45" t="s">
+        <v>125</v>
       </c>
       <c r="F80" s="14">
-        <v>32442212</v>
+        <v>6993304</v>
       </c>
       <c r="G80" s="14">
-        <v>2038</v>
-      </c>
-      <c r="H80" s="34" t="s">
-        <v>162</v>
+        <v>5043</v>
+      </c>
+      <c r="H80" s="47" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="62"/>
+      <c r="B81" s="58"/>
       <c r="C81" s="19" t="s">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="D81" s="20"/>
-      <c r="E81" s="16" t="s">
-        <v>169</v>
+      <c r="E81" s="45" t="s">
+        <v>126</v>
       </c>
       <c r="F81" s="14">
-        <v>32498324</v>
+        <v>21678790</v>
       </c>
       <c r="G81" s="14">
-        <v>2564</v>
-      </c>
-      <c r="H81" s="34" t="s">
-        <v>163</v>
+        <v>5158</v>
+      </c>
+      <c r="H81" s="47" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="B82" s="63"/>
+      <c r="B82" s="59"/>
       <c r="C82" s="19" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="D82" s="20"/>
-      <c r="E82" s="16" t="s">
-        <v>170</v>
+      <c r="E82" s="45" t="s">
+        <v>127</v>
       </c>
       <c r="F82" s="14">
-        <v>27338606</v>
+        <v>51019295</v>
       </c>
       <c r="G82" s="14">
-        <v>2141</v>
-      </c>
-      <c r="H82" s="34" t="s">
-        <v>164</v>
+        <v>5007</v>
+      </c>
+      <c r="H82" s="47" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D83" s="20"/>
-      <c r="E83" s="50" t="s">
-        <v>173</v>
-      </c>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="34"/>
+      <c r="B83" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C83" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="D83" s="54"/>
+      <c r="E83" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="37"/>
     </row>
     <row r="84" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="D84" s="20"/>
-      <c r="E84" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="34"/>
+      <c r="B84" s="53"/>
+      <c r="C84" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="D84" s="54"/>
+      <c r="E84" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="37"/>
     </row>
     <row r="85" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="D85" s="20"/>
-      <c r="E85" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="34"/>
+      <c r="B85" s="53"/>
+      <c r="C85" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" s="54"/>
+      <c r="E85" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="37"/>
     </row>
     <row r="86" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="5"/>
-      <c r="C86" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D86" s="20"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="34"/>
+      <c r="B86" s="53"/>
+      <c r="C86" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D86" s="54"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="37"/>
     </row>
     <row r="87" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="D87" s="20"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="34"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D87" s="54"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="37"/>
     </row>
     <row r="88" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D88" s="20"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="34"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D88" s="54"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="37"/>
     </row>
     <row r="89" spans="1:8" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
-      <c r="D89" s="37"/>
+      <c r="D89" s="34"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="40"/>
+      <c r="H89" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F75" xr:uid="{96205148-DF5B-4C62-ABBD-5D29C10CF543}"/>
   <mergeCells count="14">
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="B2:B15"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B16:B25"/>
     <mergeCell ref="B78:B82"/>
     <mergeCell ref="B76:B77"/>
     <mergeCell ref="B64:B70"/>
@@ -3110,17 +3134,12 @@
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="B52:B56"/>
     <mergeCell ref="B57:B63"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B16:B25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{445DCEDB-6A9D-449A-AA8C-439C228816BF}"/>
     <hyperlink ref="E6" r:id="rId2" xr:uid="{17A39B45-D4FA-4AB7-8940-D6D74436B4E3}"/>
     <hyperlink ref="E3" r:id="rId3" xr:uid="{BCC0B350-54D3-4240-B0D1-5C955AEA9988}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{66518740-1CB4-4185-BFEE-3FDDB01607DF}"/>
+    <hyperlink ref="E5" r:id="rId4" display="forgot.email1@gmail.com" xr:uid="{66518740-1CB4-4185-BFEE-3FDDB01607DF}"/>
     <hyperlink ref="E4" r:id="rId5" xr:uid="{B67CDE8E-2633-4133-B5FC-665A87FCBA0E}"/>
     <hyperlink ref="E11" r:id="rId6" xr:uid="{2E7EB3E0-4BA7-4CE7-B553-C13E8B684D39}"/>
     <hyperlink ref="E17" r:id="rId7" xr:uid="{D0CEEA64-0BE0-42B4-968C-B4EFAC82CB05}"/>
@@ -3136,55 +3155,64 @@
     <hyperlink ref="E27" r:id="rId17" xr:uid="{0568B34E-A393-4516-9C7B-D33D0994B432}"/>
     <hyperlink ref="E30" r:id="rId18" xr:uid="{05E93FC3-1B53-40F3-850A-910612D162D3}"/>
     <hyperlink ref="E31" r:id="rId19" xr:uid="{15C4002C-B085-4150-AA91-A95722CD5F9C}"/>
-    <hyperlink ref="E42" r:id="rId20" display="simply4@gmail.com" xr:uid="{8BC35477-3964-4317-B8F7-554767AFEBAE}"/>
+    <hyperlink ref="E42" r:id="rId20" display="testing123@gmail.com" xr:uid="{8BC35477-3964-4317-B8F7-554767AFEBAE}"/>
     <hyperlink ref="E43" r:id="rId21" display="simply4@gmail.com" xr:uid="{2F5C7CE6-EBB1-4985-AE92-AA230B7BA0D0}"/>
-    <hyperlink ref="E44" r:id="rId22" display="simply5@gmail.com" xr:uid="{F320A34B-83F0-48D3-B20D-4BE4401D9C52}"/>
+    <hyperlink ref="E44" r:id="rId22" display="testing234@gmail.com" xr:uid="{F320A34B-83F0-48D3-B20D-4BE4401D9C52}"/>
     <hyperlink ref="E45" r:id="rId23" display="simply5@gmail.com" xr:uid="{DFBF3D69-9EDA-470F-B750-8D7EB81985FC}"/>
     <hyperlink ref="E46" r:id="rId24" display="testing456@gmail.com" xr:uid="{E5CB3F60-341B-4E47-A3EB-4D5FCC9C9862}"/>
     <hyperlink ref="E47" r:id="rId25" display="simply5@gmail.com" xr:uid="{3C9FB2CC-805B-4CA6-B509-A5420520280C}"/>
-    <hyperlink ref="E39" r:id="rId26" xr:uid="{4D265B17-CB15-4B45-B46E-14845D6A16AB}"/>
-    <hyperlink ref="E59" r:id="rId27" xr:uid="{80D17BB9-BF25-4276-8771-34B9EAC171D1}"/>
-    <hyperlink ref="E60" r:id="rId28" xr:uid="{9ED87E8B-E71D-4753-AE8F-554EDB126343}"/>
-    <hyperlink ref="E54" r:id="rId29" xr:uid="{22EFF19B-656B-4B8C-8325-C23CBFFAE2CA}"/>
-    <hyperlink ref="E56" r:id="rId30" xr:uid="{FE2BB434-3B47-4CC6-AA73-8FC859713B2C}"/>
-    <hyperlink ref="E34" r:id="rId31" xr:uid="{D3DACB03-89E3-45ED-A7E9-FDEAE166A7B5}"/>
-    <hyperlink ref="E53" r:id="rId32" xr:uid="{5C4A2D47-A7C0-4FAC-BB5D-46B3A89CF3FE}"/>
-    <hyperlink ref="E55" r:id="rId33" xr:uid="{20459B7C-6DCB-4B01-BBA1-800CE957E9A4}"/>
-    <hyperlink ref="E36" r:id="rId34" xr:uid="{ACD5C911-DDE6-493A-BF72-10080FAB803F}"/>
-    <hyperlink ref="E15" r:id="rId35" xr:uid="{754CE5D0-FB57-435D-A72A-F5B71556605B}"/>
-    <hyperlink ref="E37" r:id="rId36" xr:uid="{E1D436D4-FF48-4A30-8BBC-80C122120C8E}"/>
-    <hyperlink ref="E50" r:id="rId37" xr:uid="{F2247F16-2565-4F01-B35A-480A808DBDF3}"/>
-    <hyperlink ref="E49" r:id="rId38" display="simply4@gmail.com" xr:uid="{89D4DA7F-893B-4AA0-8468-883415E8EE0B}"/>
-    <hyperlink ref="E35" r:id="rId39" xr:uid="{42754C57-9B3F-4988-AF3C-6DFFD113F631}"/>
-    <hyperlink ref="E24" r:id="rId40" xr:uid="{FABC0DCC-927D-4953-8CED-5FC7C1C94B7E}"/>
-    <hyperlink ref="E78" r:id="rId41" xr:uid="{520D371A-BE15-48AF-9EF5-C605DCB966AA}"/>
-    <hyperlink ref="E79" r:id="rId42" xr:uid="{2A61A99B-FECB-485A-96EF-4BE56B06F717}"/>
-    <hyperlink ref="E80" r:id="rId43" xr:uid="{3D5CD16C-B335-4097-8268-20EDB62F9003}"/>
-    <hyperlink ref="E81" r:id="rId44" xr:uid="{99830E9A-DFA6-409D-920E-D608DCD7EC83}"/>
-    <hyperlink ref="E82" r:id="rId45" xr:uid="{4D79B10F-4D29-469E-AD49-C592D75A0D48}"/>
-    <hyperlink ref="E8" r:id="rId46" xr:uid="{FB2AACCA-6426-4362-A4B0-2924FD61B151}"/>
-    <hyperlink ref="E48" r:id="rId47" display="simply4@gmail.com" xr:uid="{2A6CD140-EC42-459E-91E8-CE39A72DFCC8}"/>
-    <hyperlink ref="E84" r:id="rId48" xr:uid="{AEAB30CF-6BF7-4C89-8532-37E3DDE52411}"/>
-    <hyperlink ref="E85" r:id="rId49" xr:uid="{243345C9-8377-4F12-AF55-3B02DC8D1B8F}"/>
-    <hyperlink ref="E10" r:id="rId50" xr:uid="{74E777D6-C45F-4941-8477-D0546222FB83}"/>
-    <hyperlink ref="E83" r:id="rId51" xr:uid="{319824A4-D44E-430D-9449-E57E6752F05D}"/>
-    <hyperlink ref="E51" r:id="rId52" xr:uid="{DA82D790-63ED-410F-9F66-AE85CE900CAF}"/>
-    <hyperlink ref="E33" r:id="rId53" xr:uid="{007CA9B0-896D-408B-8B2C-38954E966151}"/>
-    <hyperlink ref="E9" r:id="rId54" xr:uid="{90A2AE7F-CDEB-4CD4-83CC-B5813E14A40D}"/>
-    <hyperlink ref="E13" r:id="rId55" xr:uid="{1418AAD4-0D4B-46B4-8A38-B301E4DB1071}"/>
-    <hyperlink ref="E52" r:id="rId56" xr:uid="{80712AAB-F6BD-44FF-A859-CB9F3061B388}"/>
-    <hyperlink ref="E61" r:id="rId57" xr:uid="{0277B7DE-173E-49E5-B013-469B58B527F0}"/>
-    <hyperlink ref="E62" r:id="rId58" xr:uid="{4F2C54DD-20ED-475A-99D2-5B5592C1E8F7}"/>
-    <hyperlink ref="E66" r:id="rId59" xr:uid="{257D4AD3-D3DA-4447-93A5-11DB48B1399E}"/>
-    <hyperlink ref="E67" r:id="rId60" xr:uid="{626C1A75-86B8-44CD-8FE3-F7CF9EDD321E}"/>
-    <hyperlink ref="E69" r:id="rId61" xr:uid="{7DADDFEA-1793-426D-85F3-EAA29E9A79B0}"/>
-    <hyperlink ref="E57" r:id="rId62" xr:uid="{BB874EF2-756E-4D00-B455-1BE5D6967288}"/>
-    <hyperlink ref="E58" r:id="rId63" xr:uid="{51757FD8-CB02-40E4-8D62-B89E52E48917}"/>
-    <hyperlink ref="E63" r:id="rId64" xr:uid="{A8081B1F-04D0-48EE-9D6A-DDC81D26DCB1}"/>
-    <hyperlink ref="E65" r:id="rId65" xr:uid="{6436D6D7-21F8-4D5D-9081-C70D87020C8E}"/>
+    <hyperlink ref="E39" r:id="rId26" display="payment.extension@gmail.com" xr:uid="{4D265B17-CB15-4B45-B46E-14845D6A16AB}"/>
+    <hyperlink ref="E56" r:id="rId27" xr:uid="{FE2BB434-3B47-4CC6-AA73-8FC859713B2C}"/>
+    <hyperlink ref="E34" r:id="rId28" xr:uid="{D3DACB03-89E3-45ED-A7E9-FDEAE166A7B5}"/>
+    <hyperlink ref="E15" r:id="rId29" xr:uid="{754CE5D0-FB57-435D-A72A-F5B71556605B}"/>
+    <hyperlink ref="E50" r:id="rId30" xr:uid="{F2247F16-2565-4F01-B35A-480A808DBDF3}"/>
+    <hyperlink ref="E49" r:id="rId31" display="simply4@gmail.com" xr:uid="{89D4DA7F-893B-4AA0-8468-883415E8EE0B}"/>
+    <hyperlink ref="E35" r:id="rId32" xr:uid="{42754C57-9B3F-4988-AF3C-6DFFD113F631}"/>
+    <hyperlink ref="E78" r:id="rId33" xr:uid="{520D371A-BE15-48AF-9EF5-C605DCB966AA}"/>
+    <hyperlink ref="E79" r:id="rId34" xr:uid="{2A61A99B-FECB-485A-96EF-4BE56B06F717}"/>
+    <hyperlink ref="E80" r:id="rId35" xr:uid="{3D5CD16C-B335-4097-8268-20EDB62F9003}"/>
+    <hyperlink ref="E81" r:id="rId36" xr:uid="{99830E9A-DFA6-409D-920E-D608DCD7EC83}"/>
+    <hyperlink ref="E82" r:id="rId37" xr:uid="{4D79B10F-4D29-469E-AD49-C592D75A0D48}"/>
+    <hyperlink ref="E8" r:id="rId38" display="ramyacgowda187@gmail.com" xr:uid="{FB2AACCA-6426-4362-A4B0-2924FD61B151}"/>
+    <hyperlink ref="E48" r:id="rId39" display="simply4@gmail.com" xr:uid="{2A6CD140-EC42-459E-91E8-CE39A72DFCC8}"/>
+    <hyperlink ref="E84" r:id="rId40" xr:uid="{AEAB30CF-6BF7-4C89-8532-37E3DDE52411}"/>
+    <hyperlink ref="E85" r:id="rId41" xr:uid="{243345C9-8377-4F12-AF55-3B02DC8D1B8F}"/>
+    <hyperlink ref="E10" r:id="rId42" xr:uid="{74E777D6-C45F-4941-8477-D0546222FB83}"/>
+    <hyperlink ref="E83" r:id="rId43" xr:uid="{319824A4-D44E-430D-9449-E57E6752F05D}"/>
+    <hyperlink ref="E33" r:id="rId44" display="ramyacgowda187@gmail.com" xr:uid="{007CA9B0-896D-408B-8B2C-38954E966151}"/>
+    <hyperlink ref="E9" r:id="rId45" xr:uid="{90A2AE7F-CDEB-4CD4-83CC-B5813E14A40D}"/>
+    <hyperlink ref="E13" r:id="rId46" xr:uid="{1418AAD4-0D4B-46B4-8A38-B301E4DB1071}"/>
+    <hyperlink ref="E57" r:id="rId47" xr:uid="{BB874EF2-756E-4D00-B455-1BE5D6967288}"/>
+    <hyperlink ref="E58" r:id="rId48" xr:uid="{51757FD8-CB02-40E4-8D62-B89E52E48917}"/>
+    <hyperlink ref="E63" r:id="rId49" xr:uid="{A8081B1F-04D0-48EE-9D6A-DDC81D26DCB1}"/>
+    <hyperlink ref="E32" r:id="rId50" xr:uid="{FBA44673-4D3C-41D3-A166-51EE27A4D7DB}"/>
+    <hyperlink ref="E7" r:id="rId51" xr:uid="{8E977BFB-DDD5-4366-8A91-8E87A0EA90B0}"/>
+    <hyperlink ref="E14" r:id="rId52" xr:uid="{90E722BD-F656-4AF6-AEAF-5373D60457A9}"/>
+    <hyperlink ref="E24" r:id="rId53" xr:uid="{7777DEA6-8CA3-4326-B6E8-26F11E487DFA}"/>
+    <hyperlink ref="E36:E38" r:id="rId54" display="residential1@gmail.com" xr:uid="{E58D25A7-BAB5-4DD6-A7A7-E059CA52DE7F}"/>
+    <hyperlink ref="E76" r:id="rId55" xr:uid="{8AC611F7-BCF2-46E3-97D4-A75B2E781805}"/>
+    <hyperlink ref="E77" r:id="rId56" xr:uid="{AA6D0C77-9948-44B4-B27E-19F3AD909880}"/>
+    <hyperlink ref="E70" r:id="rId57" xr:uid="{99A42033-015E-4056-BBAD-2C1317CFE86C}"/>
+    <hyperlink ref="E71" r:id="rId58" xr:uid="{E9283F94-AFEA-453A-90A5-F0B08A44F204}"/>
+    <hyperlink ref="E72" r:id="rId59" xr:uid="{833821FE-F77D-4267-8727-8B29D4F007F3}"/>
+    <hyperlink ref="E51" r:id="rId60" xr:uid="{4DB6E64E-4406-474F-B766-A104426B39F0}"/>
+    <hyperlink ref="E52" r:id="rId61" display="testing123@gmail.com" xr:uid="{EB007E2C-A54D-4969-9655-BF35B13C6C12}"/>
+    <hyperlink ref="E53" r:id="rId62" display="simply4@gmail.com" xr:uid="{328D936E-6EC6-4D94-A402-D63098E4A41B}"/>
+    <hyperlink ref="E61" r:id="rId63" display="testing123@gmail.com" xr:uid="{B0914A06-9747-4F81-B7F7-61FD1BBA3BE4}"/>
+    <hyperlink ref="E62" r:id="rId64" display="simply4@gmail.com" xr:uid="{E2FEE7C7-C8AC-4061-A612-17C6A28907AC}"/>
+    <hyperlink ref="E66" r:id="rId65" display="testing123@gmail.com" xr:uid="{1E4F3B0A-2BCE-49FC-A07F-136B08CDAA58}"/>
+    <hyperlink ref="E67" r:id="rId66" display="simply4@gmail.com" xr:uid="{1F652662-9EDB-4B7A-9645-7D3D4EB069D1}"/>
+    <hyperlink ref="E69" r:id="rId67" display="testing123@gmail.com" xr:uid="{45142AD8-73E2-49F2-80AC-36E99AE2DEFC}"/>
+    <hyperlink ref="E54" r:id="rId68" display="testing234@gmail.com" xr:uid="{E803252D-883A-41D1-A9D6-D4ECAEDE18BF}"/>
+    <hyperlink ref="E55" r:id="rId69" display="simply5@gmail.com" xr:uid="{B1EB35F4-5DF8-4C67-B833-FB780DC11F70}"/>
+    <hyperlink ref="E59" r:id="rId70" display="testing234@gmail.com" xr:uid="{2A3F6B1E-569C-4A75-B275-47EDF6F31C3F}"/>
+    <hyperlink ref="E60" r:id="rId71" display="simply5@gmail.com" xr:uid="{D66E74C7-4519-43B7-B7F0-0F199AFEF0C8}"/>
+    <hyperlink ref="E64" r:id="rId72" display="testing234@gmail.com" xr:uid="{014082AA-7E63-4522-B8C9-48E014953A50}"/>
+    <hyperlink ref="E65" r:id="rId73" display="simply5@gmail.com" xr:uid="{6A7A76BC-B1F1-43B3-9E07-C614EE619769}"/>
+    <hyperlink ref="E68" r:id="rId74" display="testing234@gmail.com" xr:uid="{F5607D52-E8DC-40AC-A628-D0D3892A059C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId66"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
 </worksheet>
 </file>
 
